--- a/data/trans_camb/IP1020-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 9,28</t>
+          <t>-0,24; 9,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 1,67</t>
+          <t>-3,63; 1,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 0,0</t>
+          <t>-4,76; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 5,44</t>
+          <t>-3,84; 5,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 1,89</t>
+          <t>-6,91; 1,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,61</t>
+          <t>-6,0; 0,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 5,44</t>
+          <t>-1,14; 6,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 0,93</t>
+          <t>-3,52; 1,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,4</t>
+          <t>-4,2; 0,43</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,73; 1000,32</t>
+          <t>-55,49; 954,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 3,88</t>
+          <t>-1,03; 4,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,56</t>
+          <t>0,44; 6,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 6,9</t>
+          <t>0,08; 7,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,6</t>
+          <t>-3,32; 1,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,04</t>
+          <t>-1,23; 5,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 6,38</t>
+          <t>-0,92; 6,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,86</t>
+          <t>-1,48; 1,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,61</t>
+          <t>0,5; 4,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,37</t>
+          <t>0,2; 5,07</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,55; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1034,19 +1034,19 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 1430,63</t>
+          <t>-14,27; 1361,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 1551,56</t>
+          <t>-8,84; 1305,2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 15,0</t>
+          <t>4,02; 15,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,97</t>
+          <t>0,86; 7,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 12,03</t>
+          <t>1,79; 10,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 9,11</t>
+          <t>2,21; 8,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,19</t>
+          <t>1,63; 7,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>0,0; 8,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 4,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,44</t>
+          <t>1,31; 14,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 5,73</t>
+          <t>-1,15; 4,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 6,7</t>
+          <t>-0,7; 6,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,0</t>
+          <t>-4,49; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 4,84</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,51</t>
+          <t>0,07; 4,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,01</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 5,14</t>
+          <t>-3,11; 5,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 3,13</t>
+          <t>-4,65; 3,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 7,87</t>
+          <t>-2,28; 7,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,66</t>
+          <t>0,0; 8,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,21</t>
+          <t>0,87; 11,36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 4,17</t>
+          <t>-1,41; 4,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,49</t>
+          <t>-2,22; 2,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 6,56</t>
+          <t>-0,09; 6,51</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 7,46</t>
+          <t>-1,69; 8,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 0,0</t>
+          <t>-6,45; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 6,66</t>
+          <t>-2,56; 6,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 10,24</t>
+          <t>-0,03; 10,78</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,25</t>
+          <t>-2,08; 4,11</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 6,31</t>
+          <t>-1,36; 7,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 7,12</t>
+          <t>0,06; 7,15</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,45</t>
+          <t>-2,33; 1,44</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 5,05</t>
+          <t>-1,21; 4,84</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-52,08; —</t>
+          <t>-63,53; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,14 +1903,14 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-83,63; —</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,96</t>
+          <t>-0,57; 4,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,29</t>
+          <t>-1,31; 2,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,34; 10,41</t>
+          <t>2,24; 10,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1993,17 +1993,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,22</t>
+          <t>-0,99; 2,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,72</t>
+          <t>2,73; 10,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,33</t>
+          <t>-0,35; 2,22</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,43; 9,08</t>
+          <t>3,58; 9,06</t>
         </is>
       </c>
     </row>
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-69,72; —</t>
+          <t>-70,02; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>186,58; —</t>
+          <t>184,47; —</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,24</t>
+          <t>-3,11; 0,33</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,85</t>
+          <t>-1,91; 2,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,48</t>
+          <t>-1,58; 3,39</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,12</t>
+          <t>-2,4; 1,11</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,58</t>
+          <t>-0,94; 3,67</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,32</t>
+          <t>-1,41; 3,25</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,35</t>
+          <t>-1,88; 0,35</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,11</t>
+          <t>-0,9; 2,05</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,41</t>
+          <t>-0,86; 2,55</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 884,53</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2315,27 +2315,27 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-72,9; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-97,03; 159,64</t>
+          <t>-100,0; 157,81</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 408,7</t>
+          <t>-59,58; 359,69</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-54,84; 405,92</t>
+          <t>-58,3; 404,8</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,04</t>
+          <t>0,75; 2,97</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,47</t>
+          <t>-0,37; 1,38</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,18</t>
+          <t>1,36; 4,11</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,38</t>
+          <t>-0,41; 1,47</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,9</t>
+          <t>-0,2; 1,73</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,64</t>
+          <t>1,19; 3,78</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,85</t>
+          <t>0,4; 1,85</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,35</t>
+          <t>0,05; 1,38</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,38</t>
+          <t>1,56; 3,39</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>48,72; 745,99</t>
+          <t>53,35; 727,08</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 324,19</t>
+          <t>-38,64; 275,26</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>90,64; 920,37</t>
+          <t>91,19; 1030,84</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-38,49; 260,01</t>
+          <t>-37,85; 282,23</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 346,06</t>
+          <t>-19,9; 353,11</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>85,48; 714,68</t>
+          <t>73,47; 683,91</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>37,91; 316,97</t>
+          <t>28,46; 305,26</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 251,82</t>
+          <t>0,32; 236,6</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>149,64; 594,62</t>
+          <t>126,24; 593,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1020-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 9,02</t>
+          <t>-0,27; 9,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,66</t>
+          <t>-3,76; 1,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,0</t>
+          <t>-5,62; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 5,43</t>
+          <t>-3,63; 5,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 1,01</t>
+          <t>-6,38; 1,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 0,98</t>
+          <t>-6,47; 0,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 6,0</t>
+          <t>-1,37; 5,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,18</t>
+          <t>-3,59; 1,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 0,43</t>
+          <t>-3,99; 0,43</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,49; 954,12</t>
+          <t>-58,92; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,19</t>
+          <t>-1,07; 4,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 6,63</t>
+          <t>0,47; 6,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 7,02</t>
+          <t>0,02; 7,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,16</t>
+          <t>-3,1; 1,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,52</t>
+          <t>-1,23; 5,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 6,65</t>
+          <t>-0,72; 6,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,48</t>
+          <t>-1,59; 1,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,99</t>
+          <t>0,4; 4,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 5,07</t>
+          <t>0,14; 5,24</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,55; —</t>
+          <t>-81,57; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-14,27; 1361,88</t>
+          <t>-25,04; 1446,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 1305,2</t>
+          <t>-22,64; 1685,65</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 15,03</t>
+          <t>3,98; 16,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1119,37 +1119,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,53</t>
+          <t>0,85; 8,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 10,25</t>
+          <t>1,87; 10,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 8,67</t>
+          <t>2,4; 8,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,48</t>
+          <t>1,97; 8,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,25</t>
+          <t>0,0; 7,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,61</t>
+          <t>0,0; 4,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 14,13</t>
+          <t>1,31; 11,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,97</t>
+          <t>-1,07; 5,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 6,63</t>
+          <t>-0,69; 6,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 0,0</t>
+          <t>-3,82; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>0,1; 4,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,95</t>
+          <t>0,15; 4,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>-0,12; 5,61</t>
         </is>
       </c>
     </row>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 5,19</t>
+          <t>-3,08; 5,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,16</t>
+          <t>-4,74; 3,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 7,54</t>
+          <t>-2,14; 7,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,41</t>
+          <t>0,0; 7,68</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 11,36</t>
+          <t>0,85; 9,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,77</t>
+          <t>-1,39; 4,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 2,17</t>
+          <t>-2,24; 1,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 6,51</t>
+          <t>0,2; 6,6</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 8,03</t>
+          <t>-1,73; 8,18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 0,0</t>
+          <t>-5,36; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 6,5</t>
+          <t>-2,57; 6,04</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 10,78</t>
+          <t>-0,46; 11,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 4,11</t>
+          <t>-2,07; 4,73</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 7,86</t>
+          <t>-1,27; 7,08</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,06; 7,15</t>
+          <t>0,23; 6,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,44</t>
+          <t>-2,4; 1,51</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 4,84</t>
+          <t>-0,78; 5,22</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-63,53; —</t>
+          <t>-69,52; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-83,63; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,4</t>
+          <t>-0,27; 4,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,11</t>
+          <t>-1,7; 2,05</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,24; 10,3</t>
+          <t>2,48; 10,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,87</t>
+          <t>-1,92; 0,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,23</t>
+          <t>-1,0; 1,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,73; 10,43</t>
+          <t>2,75; 10,7</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,22</t>
+          <t>-0,36; 2,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,49</t>
+          <t>-0,83; 1,58</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,58; 9,06</t>
+          <t>3,48; 9,09</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-70,02; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>184,47; —</t>
+          <t>174,41; —</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,33</t>
+          <t>-3,43; 0,35</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,01</t>
+          <t>-2,17; 1,82</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,39</t>
+          <t>-1,57; 3,57</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,11</t>
+          <t>-1,97; 1,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,67</t>
+          <t>-0,91; 3,48</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,25</t>
+          <t>-1,36; 3,38</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,35</t>
+          <t>-1,96; 0,35</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,05</t>
+          <t>-0,96; 2,07</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,55</t>
+          <t>-0,87; 2,61</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 884,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 157,81</t>
+          <t>-100,0; 113,97</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 359,69</t>
+          <t>-62,17; 386,08</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-58,3; 404,8</t>
+          <t>-61,66; 497,1</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,97</t>
+          <t>0,63; 2,92</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,38</t>
+          <t>-0,4; 1,38</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,11</t>
+          <t>1,24; 3,96</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,47</t>
+          <t>-0,33; 1,51</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,73</t>
+          <t>-0,0; 1,85</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,78</t>
+          <t>1,24; 3,7</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,85</t>
+          <t>0,49; 2,0</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,38</t>
+          <t>0,04; 1,36</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,39</t>
+          <t>1,56; 3,44</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>53,35; 727,08</t>
+          <t>36,56; 625,38</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 275,26</t>
+          <t>-41,22; 344,38</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>91,19; 1030,84</t>
+          <t>92,72; 916,96</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 282,23</t>
+          <t>-30,0; 276,77</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 353,11</t>
+          <t>-6,08; 342,84</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>73,47; 683,91</t>
+          <t>86,73; 683,46</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,46; 305,26</t>
+          <t>38,29; 339,17</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0,32; 236,6</t>
+          <t>0,36; 230,18</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>126,24; 593,56</t>
+          <t>129,02; 596,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1020-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1020-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,33</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-1,12</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,08</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,21</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 9,65</t>
+          <t>-4,62; 5,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,64</t>
+          <t>-5,95; 1,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 0,0</t>
+          <t>-5,98; 1,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 5,35</t>
+          <t>-1,1; 9,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 1,23</t>
+          <t>-4,54; 1,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 0,98</t>
+          <t>-5,68; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 5,81</t>
+          <t>-0,97; 5,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,07</t>
+          <t>-4,07; 0,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,43</t>
+          <t>-3,7; 0,56</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38,31%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-57,49%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-55,84%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>309,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-26,85%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>38,31%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-57,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-59,75%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>118,49%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-72,4%</t>
+          <t>-69,03%</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,92; —</t>
+          <t>-60,73; 1000,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,83</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,11</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,87</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,95</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,88</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,97</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,03</t>
+          <t>-3,17; 0,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,54</t>
+          <t>-0,67; 5,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 7,27</t>
+          <t>-0,65; 6,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,14</t>
+          <t>-1,01; 3,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,27</t>
+          <t>0,37; 6,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 6,21</t>
+          <t>0,9; 9,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,78</t>
+          <t>-1,32; 1,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,83</t>
+          <t>0,47; 4,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,24</t>
+          <t>0,8; 6,04</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-52,53%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>147,93%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>170,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>134,02%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>452,65%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>442,93%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-52,53%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>147,93%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>176,57%</t>
+          <t>603,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>264,41%</t>
+          <t>310,83%</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,57; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 1446,84</t>
+          <t>-13,14; 1430,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 1685,65</t>
+          <t>1,65; 1727,0</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,96</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,15</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>8,43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,02</t>
+          <t>2,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>3,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 16,14</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,09</t>
+          <t>2,08; 12,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>3,97; 15,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,58</t>
+          <t>0,83; 7,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,9</t>
+          <t>2,16; 9,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,04</t>
+          <t>1,85; 7,09</t>
         </is>
       </c>
     </row>
@@ -1167,22 +1167,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,76</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,93</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,1</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>5,29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,94</t>
+          <t>2,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,49</t>
+          <t>-0,77; 5,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,8</t>
+          <t>-0,68; 6,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,88</t>
+          <t>-3,31; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,65</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 6,56</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,0</t>
+          <t>1,51; 14,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,99</t>
+          <t>0,17; 4,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,61</t>
+          <t>0,1; 4,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 5,61</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>151,03%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>277,97%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>151,03%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>277,97%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>443,12%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>500,3%</t>
+          <t>575,44%</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,51</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,28</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,18</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>2,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 5,23</t>
+          <t>0,0; 7,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 3,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,87</t>
+          <t>0,67; 9,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,68</t>
+          <t>-3,14; 5,14</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,68; 3,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,42</t>
+          <t>-2,43; 8,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,15</t>
+          <t>-1,42; 4,17</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,51</t>
+          <t>-2,26; 1,49</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 6,6</t>
+          <t>-0,18; 6,22</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>10,85%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-0,59%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>142,34%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>144,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>396,66%</t>
+          <t>373,19%</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3,89</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1,79</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,21</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-1,28</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3,89</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 8,18</t>
+          <t>-0,27; 10,24</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 0,0</t>
+          <t>-2,09; 4,25</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 6,04</t>
+          <t>-1,33; 5,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 11,88</t>
+          <t>-1,71; 7,46</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 4,73</t>
+          <t>-7,41; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 7,08</t>
+          <t>-2,4; 7,53</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,81</t>
+          <t>-0,11; 7,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 1,51</t>
+          <t>-2,49; 1,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 5,22</t>
+          <t>-0,97; 4,87</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>375,73%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>23,63%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>173,23%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>172,83%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>101,8%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>375,73%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>23,63%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>190,35%</t>
+          <t>109,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>143,97%</t>
+          <t>139,2%</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-69,52; —</t>
+          <t>-52,08; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,42</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>7,08</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,88</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,39</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>5,61</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>5,93</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>6,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,41</t>
+          <t>-1,45; 0,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,05</t>
+          <t>-0,98; 2,22</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,48; 10,08</t>
+          <t>3,54; 12,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,87</t>
+          <t>-0,16; 4,96</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,83</t>
+          <t>-1,26; 2,29</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,75; 10,7</t>
+          <t>2,56; 10,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,34</t>
+          <t>-0,35; 2,33</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,58</t>
+          <t>-0,83; 1,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,09</t>
+          <t>3,93; 10,0</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-10,72%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>88,02%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1477,7%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>330,51%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>68,0%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>984,9%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-10,72%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>88,02%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1284,15%</t>
+          <t>1040,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1129,21%</t>
+          <t>1250,36%</t>
         </is>
       </c>
     </row>
@@ -2109,17 +2109,17 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-69,72; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>174,41; —</t>
+          <t>206,66; —</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,38</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>1,02</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-0,93</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-0,12</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,35</t>
+          <t>-2,14; 1,12</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,82</t>
+          <t>-0,85; 3,58</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,57</t>
+          <t>-1,52; 3,36</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,12</t>
+          <t>-3,43; 0,24</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,48</t>
+          <t>-2,12; 1,85</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,38</t>
+          <t>-1,56; 3,45</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,35</t>
+          <t>-1,92; 0,35</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,07</t>
+          <t>-0,99; 2,11</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,61</t>
+          <t>-0,82; 2,44</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-33,61%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>90,56%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>62,75%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-72,12%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-9,07%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>51,49%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-33,61%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>90,56%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,9; —</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,97</t>
+          <t>-97,03; 159,64</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-62,17; 386,08</t>
+          <t>-59,37; 408,7</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-61,66; 497,1</t>
+          <t>-54,32; 407,57</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>0,51</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,81</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2,52</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>1,79</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>0,53</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>0,81</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,69</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,92</t>
+          <t>-0,46; 1,38</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,38</t>
+          <t>-0,01; 1,9</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,96</t>
+          <t>1,3; 3,88</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,51</t>
+          <t>0,76; 3,04</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 1,85</t>
+          <t>-0,29; 1,47</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,7</t>
+          <t>1,59; 4,58</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,0</t>
+          <t>0,51; 1,85</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,36</t>
+          <t>0,04; 1,35</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,44</t>
+          <t>1,69; 3,69</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>56,77%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>91,04%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>281,7%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>226,84%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>66,41%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>324,27%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>56,77%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>91,04%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>264,08%</t>
+          <t>364,01%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>291,23%</t>
+          <t>318,77%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>36,56; 625,38</t>
+          <t>-38,49; 260,01</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-41,22; 344,38</t>
+          <t>-9,53; 346,06</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>92,72; 916,96</t>
+          <t>90,5; 749,85</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 276,77</t>
+          <t>48,72; 745,99</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 342,84</t>
+          <t>-28,3; 324,19</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>86,73; 683,46</t>
+          <t>109,52; 1001,72</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>38,29; 339,17</t>
+          <t>37,91; 316,97</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0,36; 230,18</t>
+          <t>-3,66; 251,82</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>129,02; 596,11</t>
+          <t>159,21; 638,68</t>
         </is>
       </c>
     </row>
